--- a/sports_forms/001_football_registration_form--sports_forms.xlsx
+++ b/sports_forms/001_football_registration_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>team_info</t>
+          <t>team_info_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Team Info</t>
+          <t>Team Info 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>player_info</t>
+          <t>player_info_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Player Info</t>
+          <t>Player Info 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>medical_clearance</t>
+          <t>medical_clearance_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Medical Clearance</t>
+          <t>Medical Clearance 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,44 +1182,61 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>medical_clearance_choices</t>
+          <t>medical_clearance_options_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>medical_clearance_choices</t>
+          <t>medical_clearance_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>medical_clearance_2_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
